--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2023_magallanes.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2023_magallanes.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$E$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$1:$E$347</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">territorio</t>
   </si>
@@ -105,6 +105,9 @@
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
+    <t xml:space="preserve">Antártica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Porvenir</t>
   </si>
   <si>
@@ -129,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:17</t>
+    <t xml:space="preserve">2026-08-28 11:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -141,16 +144,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_comunal_piramide_2023_magallanes.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Piramide de poblacion (comunal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Magallanes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
   </si>
 </sst>
 </file>
@@ -3386,13 +3398,13 @@
         <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D169" s="2" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="170">
@@ -3403,13 +3415,13 @@
         <v>6</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>221</v>
+        <v>1</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="171">
@@ -3420,13 +3432,13 @@
         <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>226</v>
+        <v>3</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="172">
@@ -3437,13 +3449,13 @@
         <v>6</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D172" s="2" t="n">
-        <v>226</v>
+        <v>1</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="173">
@@ -3454,13 +3466,13 @@
         <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="174">
@@ -3471,13 +3483,13 @@
         <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>290</v>
+        <v>1</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="175">
@@ -3485,16 +3497,16 @@
         <v>29</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D175" s="2" t="n">
-        <v>343</v>
+        <v>3</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="176">
@@ -3502,16 +3514,16 @@
         <v>29</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D176" s="2" t="n">
-        <v>322</v>
+        <v>4</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="177">
@@ -3519,16 +3531,16 @@
         <v>29</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>238</v>
+        <v>2</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="178">
@@ -3536,16 +3548,16 @@
         <v>29</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="179">
@@ -3553,16 +3565,16 @@
         <v>29</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>215</v>
+        <v>1</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="180">
@@ -3570,16 +3582,16 @@
         <v>29</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D180" s="2" t="n">
-        <v>194</v>
+        <v>1</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="181">
@@ -3587,30 +3599,30 @@
         <v>29</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>0.02</v>
@@ -3618,135 +3630,135 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D183" s="2" t="n">
-        <v>90</v>
+        <v>221</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>79</v>
+        <v>226</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D187" s="2" t="n">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D188" s="2" t="n">
-        <v>240</v>
+        <v>343</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D189" s="2" t="n">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D190" s="2" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>0.03</v>
@@ -3754,152 +3766,152 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D191" s="2" t="n">
-        <v>341</v>
+        <v>208</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D192" s="2" t="n">
-        <v>395</v>
+        <v>215</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>349</v>
+        <v>194</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>308</v>
+        <v>169</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>269</v>
+        <v>161</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>257</v>
+        <v>90</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>236</v>
+        <v>100</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>0.03</v>
@@ -3907,53 +3919,53 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>92</v>
+        <v>240</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>99</v>
+        <v>238</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="203">
@@ -3961,16 +3973,16 @@
         <v>30</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>12</v>
+        <v>239</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="204">
@@ -3978,16 +3990,16 @@
         <v>30</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>17</v>
+        <v>341</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="205">
@@ -3995,13 +4007,13 @@
         <v>30</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>30</v>
+        <v>395</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>0.05</v>
@@ -4012,16 +4024,16 @@
         <v>30</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>12</v>
+        <v>349</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="207">
@@ -4029,16 +4041,16 @@
         <v>30</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>15</v>
+        <v>308</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="208">
@@ -4046,16 +4058,16 @@
         <v>30</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>14</v>
+        <v>269</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="209">
@@ -4063,16 +4075,16 @@
         <v>30</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="210">
@@ -4080,16 +4092,16 @@
         <v>30</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>11</v>
+        <v>262</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="211">
@@ -4097,16 +4109,16 @@
         <v>30</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="212">
@@ -4114,16 +4126,16 @@
         <v>30</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>7</v>
+        <v>198</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="213">
@@ -4131,16 +4143,16 @@
         <v>30</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="214">
@@ -4148,16 +4160,16 @@
         <v>30</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="215">
@@ -4165,30 +4177,30 @@
         <v>30</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D216" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>0.02</v>
@@ -4196,47 +4208,47 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D218" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D218" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="E218" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D219" s="2" t="n">
         <v>12</v>
@@ -4247,118 +4259,118 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E225" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>0.04</v>
@@ -4366,172 +4378,172 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E227" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E228" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E229" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E230" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E231" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E232" s="2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E233" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="E234" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E235" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E236" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="237">
@@ -4539,13 +4551,13 @@
         <v>31</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E237" s="2" t="n">
         <v>0.03</v>
@@ -4556,16 +4568,16 @@
         <v>31</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E238" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="239">
@@ -4573,16 +4585,16 @@
         <v>31</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E239" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="240">
@@ -4590,16 +4602,16 @@
         <v>31</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E240" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="241">
@@ -4607,16 +4619,16 @@
         <v>31</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E241" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="242">
@@ -4624,16 +4636,16 @@
         <v>31</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E242" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="243">
@@ -4641,16 +4653,16 @@
         <v>31</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E243" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="244">
@@ -4658,13 +4670,13 @@
         <v>31</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D244" s="2" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E244" s="2" t="n">
         <v>0.04</v>
@@ -4675,16 +4687,16 @@
         <v>31</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E245" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="246">
@@ -4692,16 +4704,16 @@
         <v>31</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E246" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="247">
@@ -4709,16 +4721,16 @@
         <v>31</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E247" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="248">
@@ -4726,16 +4738,16 @@
         <v>31</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D248" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="249">
@@ -4743,282 +4755,282 @@
         <v>31</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E249" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E250" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E251" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E252" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E253" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E254" s="2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E255" s="2" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E256" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E257" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E258" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E259" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D260" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E260" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E261" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E262" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E263" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E264" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D265" s="2" t="n">
         <v>6</v>
@@ -5029,50 +5041,50 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E266" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E267" s="2" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0.01</v>
@@ -5083,16 +5095,16 @@
         <v>32</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>659</v>
+        <v>2</v>
       </c>
       <c r="E269" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="270">
@@ -5100,16 +5112,16 @@
         <v>32</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>737</v>
+        <v>7</v>
       </c>
       <c r="E270" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="271">
@@ -5117,16 +5129,16 @@
         <v>32</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>857</v>
+        <v>8</v>
       </c>
       <c r="E271" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="272">
@@ -5134,16 +5146,16 @@
         <v>32</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>838</v>
+        <v>9</v>
       </c>
       <c r="E272" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="273">
@@ -5151,13 +5163,13 @@
         <v>32</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>874</v>
+        <v>4</v>
       </c>
       <c r="E273" s="2" t="n">
         <v>0.03</v>
@@ -5168,16 +5180,16 @@
         <v>32</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>1156</v>
+        <v>4</v>
       </c>
       <c r="E274" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="275">
@@ -5185,13 +5197,13 @@
         <v>32</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>1379</v>
+        <v>8</v>
       </c>
       <c r="E275" s="2" t="n">
         <v>0.05</v>
@@ -5202,16 +5214,16 @@
         <v>32</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>1255</v>
+        <v>5</v>
       </c>
       <c r="E276" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="277">
@@ -5219,13 +5231,13 @@
         <v>32</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>978</v>
+        <v>4</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0.03</v>
@@ -5236,16 +5248,16 @@
         <v>32</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>961</v>
+        <v>6</v>
       </c>
       <c r="E278" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="279">
@@ -5253,13 +5265,13 @@
         <v>32</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>830</v>
+        <v>4</v>
       </c>
       <c r="E279" s="2" t="n">
         <v>0.03</v>
@@ -5270,16 +5282,16 @@
         <v>32</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>794</v>
+        <v>1</v>
       </c>
       <c r="E280" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="281">
@@ -5287,30 +5299,30 @@
         <v>32</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>721</v>
+        <v>2</v>
       </c>
       <c r="E281" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0.02</v>
@@ -5318,135 +5330,135 @@
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>527</v>
+        <v>737</v>
       </c>
       <c r="E283" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>396</v>
+        <v>857</v>
       </c>
       <c r="E284" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>580</v>
+        <v>838</v>
       </c>
       <c r="E285" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>682</v>
+        <v>874</v>
       </c>
       <c r="E286" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>777</v>
+        <v>1156</v>
       </c>
       <c r="E287" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>884</v>
+        <v>1379</v>
       </c>
       <c r="E288" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>865</v>
+        <v>1255</v>
       </c>
       <c r="E289" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>926</v>
+        <v>978</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0.03</v>
@@ -5454,135 +5466,135 @@
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>1172</v>
+        <v>961</v>
       </c>
       <c r="E291" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>1459</v>
+        <v>830</v>
       </c>
       <c r="E292" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>1413</v>
+        <v>794</v>
       </c>
       <c r="E293" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>1158</v>
+        <v>721</v>
       </c>
       <c r="E294" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>1076</v>
+        <v>683</v>
       </c>
       <c r="E295" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>972</v>
+        <v>527</v>
       </c>
       <c r="E296" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>836</v>
+        <v>396</v>
       </c>
       <c r="E297" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>719</v>
+        <v>580</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0.02</v>
@@ -5590,16 +5602,16 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>720</v>
+        <v>682</v>
       </c>
       <c r="E299" s="2" t="n">
         <v>0.02</v>
@@ -5607,53 +5619,53 @@
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>578</v>
+        <v>777</v>
       </c>
       <c r="E300" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>373</v>
+        <v>884</v>
       </c>
       <c r="E301" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>418</v>
+        <v>865</v>
       </c>
       <c r="E302" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="303">
@@ -5661,16 +5673,16 @@
         <v>33</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>1</v>
+        <v>926</v>
       </c>
       <c r="E303" s="2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="304">
@@ -5678,16 +5690,16 @@
         <v>33</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>5</v>
+        <v>1172</v>
       </c>
       <c r="E304" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="305">
@@ -5695,16 +5707,16 @@
         <v>33</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>6</v>
+        <v>1459</v>
       </c>
       <c r="E305" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="306">
@@ -5712,16 +5724,16 @@
         <v>33</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>5</v>
+        <v>1413</v>
       </c>
       <c r="E306" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="307">
@@ -5729,16 +5741,16 @@
         <v>33</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>6</v>
+        <v>1158</v>
       </c>
       <c r="E307" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="308">
@@ -5746,16 +5758,16 @@
         <v>33</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>16</v>
+        <v>1076</v>
       </c>
       <c r="E308" s="2" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="309">
@@ -5763,16 +5775,16 @@
         <v>33</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>11</v>
+        <v>972</v>
       </c>
       <c r="E309" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="310">
@@ -5780,13 +5792,13 @@
         <v>33</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>7</v>
+        <v>836</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0.03</v>
@@ -5797,16 +5809,16 @@
         <v>33</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>8</v>
+        <v>719</v>
       </c>
       <c r="E311" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="312">
@@ -5814,16 +5826,16 @@
         <v>33</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>8</v>
+        <v>720</v>
       </c>
       <c r="E312" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="313">
@@ -5831,16 +5843,16 @@
         <v>33</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>7</v>
+        <v>578</v>
       </c>
       <c r="E313" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="314">
@@ -5848,16 +5860,16 @@
         <v>33</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>5</v>
+        <v>373</v>
       </c>
       <c r="E314" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="315">
@@ -5865,13 +5877,13 @@
         <v>33</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>2</v>
+        <v>418</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0.01</v>
@@ -5879,13 +5891,13 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D316" s="2" t="n">
         <v>1</v>
@@ -5896,50 +5908,50 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E317" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E318" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0.02</v>
@@ -5947,64 +5959,64 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E320" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E321" s="2" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C322" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D322" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D322" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="E322" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D323" s="2" t="n">
         <v>7</v>
@@ -6015,193 +6027,414 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E324" s="2" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E325" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E326" s="2" t="n">
-        <v>0.07</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E327" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E328" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E329" s="2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E330" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E331" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E332" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E333" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0.01</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C335" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D335" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D336" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E336" s="2" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C337" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D337" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E337" s="2" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C338" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D338" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E338" s="2" t="n">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C339" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D339" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E339" s="2" t="n">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C340" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D340" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E340" s="2" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C341" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D341" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E341" s="2" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C342" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D342" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E342" s="2" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C343" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D343" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E343" s="2" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C344" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D344" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E344" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C345" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D345" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E345" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C346" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D346" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E346" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C347" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D347" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E347" s="2" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E334"/>
+  <autoFilter ref="A1:E347"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -6218,58 +6451,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2023_magallanes.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2023_magallanes.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:15</t>
+    <t xml:space="preserve">2026-09-06 17:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
